--- a/ListaDeCompras.xlsx
+++ b/ListaDeCompras.xlsx
@@ -60,9 +60,6 @@
     <t>https://es.aliexpress.com/item/4000867583795.html?spm=a2g0o.productlist.main.32.1276pPQapPQaui&amp;algo_pvid=dc9e8a46-7765-4d1a-8f14-6debd841fdb2&amp;algo_exp_id=dc9e8a46-7765-4d1a-8f14-6debd841fdb2-29&amp;pdp_ext_f=%7B%22order%22%3A%223376%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21USD%214.37%214.37%21%21%214.37%214.37%21%40212a70c017746509071598145e3de4%2110000009746956243%21sea%21PY%210%21ABX%211%210%21n_tag%3A-29910%3Bd%3A78b3009%3Bm03_new_user%3A-29895&amp;curPageLogUid=YPG3fmZDelMp&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A4000867583795%7C_p_origin_prod%3A</t>
   </si>
   <si>
-    <t>Conector USB tipo C puerto de carga hembra Jack 2/4/6/16 Pin tipo C enchufe PCB soldadura SMD SMT DIY reparación tipo C adaptador - AliExpress</t>
-  </si>
-  <si>
     <t>DRIVERS</t>
   </si>
   <si>
@@ -90,9 +87,6 @@
     <t>TS-1088-AR02016 SMD 10U</t>
   </si>
   <si>
-    <t>USB-C 10U</t>
-  </si>
-  <si>
     <t>B330-13-F</t>
   </si>
   <si>
@@ -304,6 +298,12 @@
   </si>
   <si>
     <t>https://es.aliexpress.com/item/32618031228.html?spm=a2g0o.productlist.main.2.47d1mln5mln5lv&amp;algo_pvid=aaf98f6c-ef7a-4dfb-8837-6d57d388a6a4&amp;algo_exp_id=aaf98f6c-ef7a-4dfb-8837-6d57d388a6a4-1&amp;pdp_ext_f=%7B%22order%22%3A%221812%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21USD%211.99%211.29%21%21%211.99%211.29%21%402101529317748185469996252eea15%2112000030225248944%21sea%21PY%210%21ABX%211%210%21n_tag%3A-29910%3Bd%3A78b3009%3Bm03_new_user%3A-29895&amp;curPageLogUid=pLduYfAZWpfP&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A32618031228%7C_p_origin_prod%3A</t>
+  </si>
+  <si>
+    <t>https://www.mouser.com/ProductDetail/GCT/USB4105-GF-A?qs=KUoIvG%2F9IlY%2FMLlBMpStpA%3D%3D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USB-C </t>
   </si>
 </sst>
 </file>
@@ -728,7 +728,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B1" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -778,7 +778,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C4">
         <v>1</v>
@@ -800,20 +800,20 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5">
-        <v>1.1299999999999999</v>
+        <v>0.94</v>
       </c>
       <c r="E5">
         <f t="shared" si="0"/>
-        <v>1.1299999999999999</v>
+        <v>1.88</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>14</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -822,7 +822,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -835,7 +835,7 @@
         <v>0.93</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -844,7 +844,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -857,7 +857,7 @@
         <v>0.63</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -866,7 +866,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C8">
         <v>1</v>
@@ -879,7 +879,7 @@
         <v>1.85</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -888,7 +888,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -901,7 +901,7 @@
         <v>1.29</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -910,7 +910,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C10">
         <v>2</v>
@@ -923,7 +923,7 @@
         <v>1.08</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -932,7 +932,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -945,7 +945,7 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -954,7 +954,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C12">
         <v>2</v>
@@ -967,7 +967,7 @@
         <v>0.52</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
@@ -976,7 +976,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C13">
         <v>2</v>
@@ -989,7 +989,7 @@
         <v>0.2</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -998,7 +998,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C14">
         <v>2</v>
@@ -1011,7 +1011,7 @@
         <v>0.2</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -1020,7 +1020,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C15">
         <v>2</v>
@@ -1033,7 +1033,7 @@
         <v>0.2</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -1042,7 +1042,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C16">
         <v>4</v>
@@ -1055,7 +1055,7 @@
         <v>0.4</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -1064,7 +1064,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C17">
         <v>2</v>
@@ -1077,7 +1077,7 @@
         <v>6.8</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
@@ -1085,16 +1085,16 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="D19" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E19" s="5">
         <f>SUM(E3:E17)</f>
-        <v>28.039999999999992</v>
+        <v>28.789999999999992</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B22" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E22" s="2"/>
       <c r="G22" s="1"/>
@@ -1104,7 +1104,7 @@
         <v>0</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>2</v>
@@ -1146,7 +1146,7 @@
         <v>2</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -1159,7 +1159,7 @@
         <v>0.9</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -1168,7 +1168,7 @@
         <v>3</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C26">
         <v>1</v>
@@ -1181,7 +1181,7 @@
         <v>21.58</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
@@ -1190,7 +1190,7 @@
         <v>4</v>
       </c>
       <c r="B27" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C27">
         <v>3</v>
@@ -1203,7 +1203,7 @@
         <v>1.0499999999999998</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
@@ -1212,7 +1212,7 @@
         <v>5</v>
       </c>
       <c r="B28" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C28">
         <v>3</v>
@@ -1225,7 +1225,7 @@
         <v>7.62</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -1234,7 +1234,7 @@
         <v>6</v>
       </c>
       <c r="B29" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C29">
         <v>6</v>
@@ -1247,7 +1247,7 @@
         <v>0.84000000000000008</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -1256,7 +1256,7 @@
         <v>7</v>
       </c>
       <c r="B30" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C30">
         <v>3</v>
@@ -1269,7 +1269,7 @@
         <v>0.69000000000000006</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
@@ -1278,7 +1278,7 @@
         <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C31">
         <v>3</v>
@@ -1291,7 +1291,7 @@
         <v>0.30000000000000004</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
@@ -1300,7 +1300,7 @@
         <v>9</v>
       </c>
       <c r="B32" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C32">
         <v>6</v>
@@ -1313,7 +1313,7 @@
         <v>1.2000000000000002</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
@@ -1322,7 +1322,7 @@
         <v>10</v>
       </c>
       <c r="B33" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C33">
         <v>3</v>
@@ -1335,7 +1335,7 @@
         <v>6.75</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -1344,7 +1344,7 @@
         <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C34">
         <v>3</v>
@@ -1357,7 +1357,7 @@
         <v>0.30000000000000004</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -1366,7 +1366,7 @@
         <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C35">
         <v>3</v>
@@ -1379,12 +1379,12 @@
         <v>0.30000000000000004</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D37" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E37" s="5">
         <f>SUM(E24:E35)</f>
@@ -1393,7 +1393,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B40" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -1401,7 +1401,7 @@
         <v>0</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C41" s="7" t="s">
         <v>2</v>
@@ -1421,7 +1421,7 @@
         <v>1</v>
       </c>
       <c r="B42" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -1434,7 +1434,7 @@
         <v>3</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -1443,7 +1443,7 @@
         <v>2</v>
       </c>
       <c r="B43" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C43">
         <v>1</v>
@@ -1456,7 +1456,7 @@
         <v>1.04</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -1465,7 +1465,7 @@
         <v>3</v>
       </c>
       <c r="B44" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C44">
         <v>2</v>
@@ -1478,7 +1478,7 @@
         <v>0.34</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -1487,7 +1487,7 @@
         <v>4</v>
       </c>
       <c r="B45" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -1500,7 +1500,7 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -1509,7 +1509,7 @@
         <v>5</v>
       </c>
       <c r="B46" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C46">
         <v>1</v>
@@ -1522,7 +1522,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -1553,7 +1553,7 @@
         <v>7</v>
       </c>
       <c r="B48" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C48">
         <v>4</v>
@@ -1566,7 +1566,7 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -1575,7 +1575,7 @@
         <v>8</v>
       </c>
       <c r="B49" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C49">
         <v>6</v>
@@ -1588,7 +1588,7 @@
         <v>3.24</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -1597,7 +1597,7 @@
         <v>9</v>
       </c>
       <c r="B50" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C50">
         <v>2</v>
@@ -1610,7 +1610,7 @@
         <v>1.04</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
@@ -1619,7 +1619,7 @@
         <v>10</v>
       </c>
       <c r="B51" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C51">
         <v>2</v>
@@ -1632,7 +1632,7 @@
         <v>0.52</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
@@ -1641,7 +1641,7 @@
         <v>11</v>
       </c>
       <c r="B52" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C52">
         <v>2</v>
@@ -1654,7 +1654,7 @@
         <v>0.36</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -1663,7 +1663,7 @@
         <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C53">
         <v>2</v>
@@ -1676,7 +1676,7 @@
         <v>0.94</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
@@ -1685,7 +1685,7 @@
         <v>13</v>
       </c>
       <c r="B54" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C54">
         <v>2</v>
@@ -1698,7 +1698,7 @@
         <v>0.22</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -1707,7 +1707,7 @@
         <v>14</v>
       </c>
       <c r="B55" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C55">
         <v>2</v>
@@ -1720,7 +1720,7 @@
         <v>0.22</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
@@ -1729,7 +1729,7 @@
         <v>15</v>
       </c>
       <c r="B56" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C56">
         <v>2</v>
@@ -1742,7 +1742,7 @@
         <v>0.2</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
@@ -1751,7 +1751,7 @@
         <v>16</v>
       </c>
       <c r="B57" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C57">
         <v>2</v>
@@ -1764,7 +1764,7 @@
         <v>0.2</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
@@ -1773,7 +1773,7 @@
         <v>17</v>
       </c>
       <c r="B58" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C58">
         <v>2</v>
@@ -1786,7 +1786,7 @@
         <v>0.2</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
@@ -1795,7 +1795,7 @@
         <v>18</v>
       </c>
       <c r="B59" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -1808,7 +1808,7 @@
         <v>0.1</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
@@ -1817,7 +1817,7 @@
         <v>19</v>
       </c>
       <c r="B60" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C60">
         <v>1</v>
@@ -1830,12 +1830,12 @@
         <v>0.1</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D62" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E62" s="5">
         <f>SUM(E42:E60)</f>
@@ -1844,7 +1844,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B64" s="6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
@@ -1852,7 +1852,7 @@
         <v>0</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C65" s="7" t="s">
         <v>2</v>
@@ -1872,7 +1872,7 @@
         <v>1</v>
       </c>
       <c r="B66" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C66">
         <v>1</v>
@@ -1894,7 +1894,7 @@
         <v>2</v>
       </c>
       <c r="B67" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -1907,12 +1907,12 @@
         <v>8.44</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D69" s="5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E69" s="5">
         <f>SUM(E66:E67)</f>
@@ -1921,18 +1921,18 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="D71" s="5" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E71" s="5">
         <f>E19+E37+E62+E69</f>
-        <v>112.58999999999999</v>
+        <v>113.33999999999999</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F3" r:id="rId1"/>
     <hyperlink ref="F4" r:id="rId2" display="https://es.aliexpress.com/item/1005007460897865.html?spm=a2g0o.productlist.main.4.3fa85507sRvbg8&amp;aem_p4p_detail=202603271521052464294803219820000572873&amp;algo_pvid=cdcd1a6d-f976-4060-b3bb-55710f6ac72b&amp;algo_exp_id=cdcd1a6d-f976-4060-b3bb-55710f6ac72b-3&amp;pdp_ext_f=%7B%22order%22%3A%2234760%22%2C%22spu_best_type%22%3A%22price%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21USD%210.99%210.77%21%21%210.99%210.77%21%4021015b7d17746500655427707ebfba%2112000040853255020%21sea%21PY%210%21ABX%211%210%21n_tag%3A-29910%3Bd%3A78b3009%3Bm03_new_user%3A-29895&amp;curPageLogUid=QL9FQO7aCmdz&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005007460897865%7C_p_origin_prod%3A&amp;search_p4p_id=202603271521052464294803219820000572873_1"/>
-    <hyperlink ref="F5" r:id="rId3" display="https://es.aliexpress.com/item/1005009438498535.html?spm=a2g0o.productlist.main.1.284b582f582fm1&amp;algo_pvid=ac212364-9bf5-46fa-9bd2-1233278e7c36&amp;algo_exp_id=ac212364-9bf5-46fa-9bd2-1233278e7c36-0&amp;pdp_ext_f=%7B%22order%22%3A%221019%22%2C%22spu_best_type%22%3A%22price%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21USD%211.02%210.99%21%21%217.00%216.79%21%40212a70c017746836407734439e3e1d%2112000049098613157%21sea%21PY%210%21ABX%211%210%21n_tag%3A-29910%3Bd%3A78b3009%3Bm03_new_user%3A-29895&amp;curPageLogUid=GkJJS2D465Ko&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005009438498535%7C_p_origin_prod%3A"/>
+    <hyperlink ref="F5" r:id="rId3"/>
     <hyperlink ref="F25" r:id="rId4"/>
     <hyperlink ref="F6" r:id="rId5" display="https://es.aliexpress.com/item/1005011943648412.html?spm=a2g0o.productlist.main.1.6c59fDMrfDMrTS&amp;algo_pvid=36fc4f25-e0e5-4119-a004-d99721300602&amp;algo_exp_id=36fc4f25-e0e5-4119-a004-d99721300602-0&amp;pdp_ext_f=%7B%22order%22%3A%22-1%22%2C%22eval%22%3A%221%22%2C%22fromPage%22%3A%22search%22%7D&amp;pdp_npi=6%40dis%21USD%211.86%210.93%21%21%2112.80%216.40%21%402102f0c917746869817147639eb613%2112000057086321431%21sea%21PY%210%21ABX%211%210%21n_tag%3A-29910%3Bd%3A78b3009%3Bm03_new_user%3A-29895&amp;curPageLogUid=kW8MJiTtlRvl&amp;utparam-url=scene%3Asearch%7Cquery_from%3A%7Cx_object_id%3A1005011943648412%7C_p_origin_prod%3A"/>
     <hyperlink ref="F7" r:id="rId6"/>
